--- a/dati.xlsx
+++ b/dati.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Angelo\Desktop\App FASCICOLI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angelo.giangrandi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AED145B7-129B-44C3-A3B9-355A84796051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBF46F8-DE56-4C26-9810-863DAB176DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{6735586A-DA8C-4CB3-995F-2DC5913EBDDC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6735586A-DA8C-4CB3-995F-2DC5913EBDDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="7">
   <si>
     <t>ANNO</t>
   </si>
@@ -56,12 +53,15 @@
   <si>
     <t>MICHELE</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,16 +69,60 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -86,12 +130,77 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -110,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -150,7 +259,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -256,7 +365,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -398,7 +507,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -406,118 +515,877 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB3E45B7-102D-4317-8A4F-2320D1D042BF}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2026</v>
-      </c>
-      <c r="B2">
-        <v>1112</v>
-      </c>
-      <c r="C2">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2022</v>
-      </c>
-      <c r="B3">
-        <v>354</v>
-      </c>
-      <c r="C3">
-        <v>44</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2020</v>
-      </c>
-      <c r="B4">
-        <v>54</v>
-      </c>
-      <c r="C4">
-        <v>45</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="12">
+        <v>5246</v>
+      </c>
+      <c r="C2" s="3">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B3" s="2">
+        <v>502</v>
+      </c>
+      <c r="C3" s="1">
+        <v>44</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1525</v>
+      </c>
+      <c r="C4" s="5">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2782</v>
+      </c>
+      <c r="C5" s="1">
+        <v>44</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3306</v>
+      </c>
+      <c r="C6" s="7">
+        <v>44</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>2025</v>
       </c>
-      <c r="B5">
-        <v>5566</v>
-      </c>
-      <c r="C5">
-        <v>44</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2024</v>
-      </c>
-      <c r="B6">
-        <v>524</v>
-      </c>
-      <c r="C6">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2026</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2026</v>
-      </c>
-      <c r="B8">
-        <v>5554</v>
-      </c>
-      <c r="C8">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B7" s="2">
+        <v>2910</v>
+      </c>
+      <c r="C7" s="1">
+        <v>21</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="7">
+        <v>3350</v>
+      </c>
+      <c r="C8" s="8">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="7">
+        <v>3387</v>
+      </c>
+      <c r="C9" s="7">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3605</v>
+      </c>
+      <c r="C10" s="3">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="2">
+        <v>4229</v>
+      </c>
+      <c r="C11" s="3">
+        <v>21</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B12" s="2">
+        <v>4283</v>
+      </c>
+      <c r="C12" s="1">
+        <v>21</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="2">
+        <v>4717</v>
+      </c>
+      <c r="C13" s="1">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B14" s="9">
+        <v>5006</v>
+      </c>
+      <c r="C14" s="1">
+        <v>21</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="2">
+        <v>5316</v>
+      </c>
+      <c r="C15" s="1">
+        <v>21</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="5">
+        <v>6051</v>
+      </c>
+      <c r="C16" s="5">
+        <v>21</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1812</v>
+      </c>
+      <c r="C17" s="1">
+        <v>44</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3918</v>
+      </c>
+      <c r="C18" s="1">
+        <v>44</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="7">
+        <v>3953</v>
+      </c>
+      <c r="C19" s="7">
+        <v>44</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1158</v>
+      </c>
+      <c r="C20" s="7">
+        <v>21</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1271</v>
+      </c>
+      <c r="C21" s="1">
+        <v>21</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1580</v>
+      </c>
+      <c r="C22" s="3">
+        <v>21</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="9">
+        <v>1627</v>
+      </c>
+      <c r="C23" s="3">
+        <v>21</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1794</v>
+      </c>
+      <c r="C24" s="3">
+        <v>21</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1794</v>
+      </c>
+      <c r="C25" s="3">
+        <v>21</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="9">
+        <v>2012</v>
+      </c>
+      <c r="C26" s="3">
+        <v>21</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2355</v>
+      </c>
+      <c r="C27" s="3">
+        <v>21</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2445</v>
+      </c>
+      <c r="C28" s="3">
+        <v>21</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2643</v>
+      </c>
+      <c r="C29" s="3">
+        <v>21</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B30" s="10">
+        <v>2684</v>
+      </c>
+      <c r="C30" s="3">
+        <v>21</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2733</v>
+      </c>
+      <c r="C31" s="3">
+        <v>21</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2783</v>
+      </c>
+      <c r="C32" s="3">
+        <v>21</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B33" s="2">
+        <v>3007</v>
+      </c>
+      <c r="C33" s="3">
+        <v>21</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B34" s="2">
+        <v>3041</v>
+      </c>
+      <c r="C34" s="3">
+        <v>21</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B35" s="2">
+        <v>3083</v>
+      </c>
+      <c r="C35" s="3">
+        <v>21</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B36" s="2">
+        <v>3096</v>
+      </c>
+      <c r="C36" s="3">
+        <v>21</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="2">
+        <v>3130</v>
+      </c>
+      <c r="C37" s="3">
+        <v>21</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="2">
+        <v>3155</v>
+      </c>
+      <c r="C38" s="3">
+        <v>21</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B39" s="2">
+        <v>3366</v>
+      </c>
+      <c r="C39" s="3">
+        <v>21</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B40" s="2">
+        <v>3381</v>
+      </c>
+      <c r="C40" s="3">
+        <v>21</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="2">
+        <v>3395</v>
+      </c>
+      <c r="C41" s="3">
+        <v>21</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="2">
+        <v>3398</v>
+      </c>
+      <c r="C42" s="3">
+        <v>21</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="2">
+        <v>3449</v>
+      </c>
+      <c r="C43" s="1">
+        <v>21</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="2">
+        <v>3454</v>
+      </c>
+      <c r="C44" s="1">
+        <v>21</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B45" s="2">
+        <v>3548</v>
+      </c>
+      <c r="C45" s="1">
+        <v>21</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B46" s="2">
+        <v>3592</v>
+      </c>
+      <c r="C46" s="1">
+        <v>21</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B47" s="2">
+        <v>3592</v>
+      </c>
+      <c r="C47" s="1">
+        <v>21</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B48" s="2">
+        <v>3598</v>
+      </c>
+      <c r="C48" s="1">
+        <v>21</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B49" s="2">
+        <v>3622</v>
+      </c>
+      <c r="C49" s="1">
+        <v>21</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B50" s="7">
+        <v>3651</v>
+      </c>
+      <c r="C50" s="1">
+        <v>21</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B51" s="2">
+        <v>3677</v>
+      </c>
+      <c r="C51" s="1">
+        <v>21</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B52" s="2">
+        <v>3718</v>
+      </c>
+      <c r="C52" s="1">
+        <v>21</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B53" s="9">
+        <v>3744</v>
+      </c>
+      <c r="C53" s="1">
+        <v>21</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B54" s="7">
+        <v>732</v>
+      </c>
+      <c r="C54" s="7">
+        <v>25</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B55" s="1">
+        <v>947</v>
+      </c>
+      <c r="C55" s="1">
+        <v>44</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1370</v>
+      </c>
+      <c r="C56" s="1">
+        <v>44</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B57" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C57" s="1">
+        <v>44</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="2">
+        <v>2169</v>
+      </c>
+      <c r="C58" s="1">
+        <v>44</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B59" s="2">
+        <v>2238</v>
+      </c>
+      <c r="C59" s="1">
+        <v>44</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B60" s="2">
+        <v>2345</v>
+      </c>
+      <c r="C60" s="1">
+        <v>44</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B61" s="11">
+        <v>2346</v>
+      </c>
+      <c r="C61" s="4">
+        <v>44</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B62" s="1">
+        <v>2503</v>
+      </c>
+      <c r="C62" s="1">
+        <v>44</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
